--- a/reports/telegram/aegis_daily_2026-08-13.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-13.xlsx
@@ -880,7 +880,7 @@
         <v>548.4</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AN2" s="3" t="n">
         <v>-1.66</v>
@@ -905,7 +905,7 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
         <v>2445.7</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>0</v>
+        <v>-3.93</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>3.16</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
         <v>11896</v>
       </c>
       <c r="AM4" s="5" t="n">
-        <v>0</v>
+        <v>-1.82</v>
       </c>
       <c r="AN4" s="5" t="n">
         <v>7.36</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1314,43 +1314,43 @@
         </is>
       </c>
       <c r="AB5" s="3" t="n">
-        <v>1429.6</v>
+        <v>1431.7</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>1438.5</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1358.12</v>
+        <v>1360.115</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>-5.59</v>
+        <v>-5.45</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>1611.42</v>
+        <v>1613.56</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>12.02</v>
+        <v>12.17</v>
       </c>
       <c r="AL5" s="3" t="n">
         <v>1429.6</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-0.62</v>
+        <v>-0.47</v>
       </c>
       <c r="AO5" s="3" t="n">
         <v>0</v>
@@ -1368,11 +1368,11 @@
         <v>5</v>
       </c>
       <c r="AT5" s="3" t="n">
-        <v>4.69</v>
+        <v>4.83</v>
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="V6" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="W6" s="3" t="inlineStr"/>
       <c r="X6" s="3" t="n">
@@ -1461,43 +1461,43 @@
         </is>
       </c>
       <c r="AB6" s="3" t="n">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>2014.8</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>1844.9</v>
+        <v>1846.8</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-8.43</v>
+        <v>-8.34</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>2173.17</v>
+        <v>2175.31</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>7.86</v>
+        <v>7.97</v>
       </c>
       <c r="AL6" s="3" t="n">
         <v>1942</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>-3.61</v>
+        <v>-3.51</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>0</v>
@@ -1515,11 +1515,11 @@
         <v>5</v>
       </c>
       <c r="AT6" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="AU6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.7% ≤ -5.0% · exit</t>
+          <t>WARNING·STOP_LOSS_HIT·-5.6% ≤ -5.0% · exit</t>
         </is>
       </c>
       <c r="T7" s="3" t="n">
@@ -1612,43 +1612,43 @@
         </is>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>2278.9</v>
+        <v>2281</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>2417</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>2164.955</v>
+        <v>2166.95</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-10.43</v>
+        <v>-10.35</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>2461.212</v>
+        <v>2463.48</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>2633.496840000001</v>
+        <v>2635.9236</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="AL7" s="3" t="n">
         <v>2278.9</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-5.71</v>
+        <v>-5.63</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>1.24</v>
@@ -1666,11 +1666,11 @@
         <v>5</v>
       </c>
       <c r="AT7" s="3" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1759,43 +1759,43 @@
         </is>
       </c>
       <c r="AB8" s="3" t="n">
-        <v>1685.8</v>
+        <v>1701.5</v>
       </c>
       <c r="AC8" s="3" t="n">
         <v>1625.5</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>1632</v>
+        <v>1647</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>1740</v>
+        <v>1756</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>1601.51</v>
+        <v>1616.425</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-1.48</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>1709</v>
+        <v>1725</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>5.14</v>
+        <v>6.12</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>1828.63</v>
+        <v>1845.75</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>12.5</v>
+        <v>13.55</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>1685.8</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>3.71</v>
+        <v>4.68</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>0</v>
@@ -1813,11 +1813,11 @@
         <v>5</v>
       </c>
       <c r="AT8" s="3" t="n">
-        <v>5.14</v>
+        <v>6.12</v>
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 4→5 · Conf 72% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.4%) · Rank ↓ 4→5 · Conf 71% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="V9" s="7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W9" s="7" t="inlineStr"/>
       <c r="X9" s="7" t="n">
@@ -1906,43 +1906,43 @@
         </is>
       </c>
       <c r="AB9" s="7" t="n">
-        <v>338.5</v>
+        <v>339.5</v>
       </c>
       <c r="AC9" s="7" t="n">
         <v>345.75</v>
       </c>
       <c r="AD9" s="7" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AE9" s="7" t="n">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AF9" s="7" t="n">
-        <v>321.575</v>
+        <v>322.525</v>
       </c>
       <c r="AG9" s="7" t="n">
-        <v>-6.99</v>
+        <v>-6.72</v>
       </c>
       <c r="AH9" s="7" t="n">
-        <v>365.58</v>
+        <v>366.66</v>
       </c>
       <c r="AI9" s="7" t="n">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="AJ9" s="7" t="n">
-        <v>391.1706000000001</v>
+        <v>392.3262</v>
       </c>
       <c r="AK9" s="7" t="n">
-        <v>13.14</v>
+        <v>13.47</v>
       </c>
       <c r="AL9" s="7" t="n">
         <v>338.45</v>
       </c>
       <c r="AM9" s="7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AN9" s="7" t="n">
-        <v>-2.1</v>
+        <v>-1.81</v>
       </c>
       <c r="AO9" s="7" t="n">
         <v>0</v>
@@ -1960,11 +1960,11 @@
         <v>5</v>
       </c>
       <c r="AT9" s="7" t="n">
-        <v>5.74</v>
+        <v>6.05</v>
       </c>
       <c r="AU9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -2022,16 +2022,16 @@
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↑ 7→6 · Conf 68% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.4%) · Rank ↑ 7→6 · Conf 69% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.3% ≤ -5.0% · exit</t>
+          <t>WARNING·STOP_LOSS_HIT·-5.7% ≤ -5.0% · exit</t>
         </is>
       </c>
       <c r="T10" s="7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="V10" s="7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="W10" s="7" t="inlineStr"/>
       <c r="X10" s="7" t="n">
@@ -2057,43 +2057,43 @@
         </is>
       </c>
       <c r="AB10" s="7" t="n">
-        <v>268</v>
+        <v>269.5</v>
       </c>
       <c r="AC10" s="7" t="n">
         <v>285.9</v>
       </c>
       <c r="AD10" s="7" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE10" s="7" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AF10" s="7" t="n">
-        <v>254.6</v>
+        <v>256.025</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>-10.95</v>
+        <v>-10.45</v>
       </c>
       <c r="AH10" s="7" t="n">
-        <v>289.44</v>
+        <v>291.06</v>
       </c>
       <c r="AI10" s="7" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="AJ10" s="7" t="n">
-        <v>309.7008</v>
+        <v>311.4342</v>
       </c>
       <c r="AK10" s="7" t="n">
-        <v>8.32</v>
+        <v>8.93</v>
       </c>
       <c r="AL10" s="7" t="n">
         <v>267.95</v>
       </c>
       <c r="AM10" s="7" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN10" s="7" t="n">
-        <v>-6.26</v>
+        <v>-5.74</v>
       </c>
       <c r="AO10" s="7" t="n">
         <v>0</v>
@@ -2111,11 +2111,11 @@
         <v>5</v>
       </c>
       <c r="AT10" s="7" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="AU10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="AB11" s="7" t="n">
-        <v>405.9</v>
+        <v>405.7</v>
       </c>
       <c r="AC11" s="7" t="n">
         <v>388.7</v>
@@ -2216,31 +2216,31 @@
         <v>418</v>
       </c>
       <c r="AF11" s="7" t="n">
-        <v>385.605</v>
+        <v>385.415</v>
       </c>
       <c r="AG11" s="7" t="n">
-        <v>-0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="AH11" s="7" t="n">
-        <v>438.372</v>
+        <v>438.156</v>
       </c>
       <c r="AI11" s="7" t="n">
-        <v>12.78</v>
+        <v>12.72</v>
       </c>
       <c r="AJ11" s="7" t="n">
-        <v>469.0580400000001</v>
+        <v>468.82692</v>
       </c>
       <c r="AK11" s="7" t="n">
-        <v>20.67</v>
+        <v>20.61</v>
       </c>
       <c r="AL11" s="7" t="n">
         <v>405.85</v>
       </c>
       <c r="AM11" s="7" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AN11" s="7" t="n">
-        <v>4.43</v>
+        <v>4.37</v>
       </c>
       <c r="AO11" s="7" t="n">
         <v>0</v>
@@ -2258,301 +2258,301 @@
         <v>5</v>
       </c>
       <c r="AT11" s="7" t="n">
-        <v>12.78</v>
+        <v>12.72</v>
       </c>
       <c r="AU11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>ITC_IND_20260731</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>IRCTC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K12" s="7" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr"/>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
-      <c r="Q12" s="7" t="inlineStr"/>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank #8 · Conf 72% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr"/>
-      <c r="T12" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→8 · Conf 67% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V12" s="7" t="n">
+      <c r="V12" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="W12" s="7" t="inlineStr"/>
-      <c r="X12" s="7" t="n">
+      <c r="W12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="Y12" s="7" t="n">
+      <c r="Y12" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="Z12" s="7" t="n">
+      <c r="Z12" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="AA12" s="7" t="inlineStr">
+      <c r="AA12" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AB12" s="7" t="n">
-        <v>279</v>
-      </c>
-      <c r="AC12" s="7" t="n">
-        <v>282.9</v>
-      </c>
-      <c r="AD12" s="7" t="n">
-        <v>272</v>
-      </c>
-      <c r="AE12" s="7" t="n">
-        <v>286</v>
-      </c>
-      <c r="AF12" s="7" t="n">
-        <v>265.05</v>
-      </c>
-      <c r="AG12" s="7" t="n">
-        <v>-6.31</v>
-      </c>
-      <c r="AH12" s="7" t="n">
-        <v>280</v>
-      </c>
-      <c r="AI12" s="7" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="AJ12" s="7" t="n">
-        <v>299.6</v>
-      </c>
-      <c r="AK12" s="7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AL12" s="7" t="n">
-        <v>279</v>
-      </c>
-      <c r="AM12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="7" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="AO12" s="7" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AP12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="7" t="inlineStr"/>
-      <c r="AR12" s="7" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AS12" s="7" t="n">
+      <c r="AB12" s="5" t="n">
+        <v>513.5</v>
+      </c>
+      <c r="AC12" s="5" t="n">
+        <v>494.35</v>
+      </c>
+      <c r="AD12" s="5" t="n">
+        <v>498</v>
+      </c>
+      <c r="AE12" s="5" t="n">
+        <v>529</v>
+      </c>
+      <c r="AF12" s="5" t="n">
+        <v>487.825</v>
+      </c>
+      <c r="AG12" s="5" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="AH12" s="5" t="n">
+        <v>554.58</v>
+      </c>
+      <c r="AI12" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AJ12" s="5" t="n">
+        <v>593.4006000000001</v>
+      </c>
+      <c r="AK12" s="5" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AL12" s="5" t="n">
+        <v>515.05</v>
+      </c>
+      <c r="AM12" s="5" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AN12" s="5" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AO12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="5" t="inlineStr"/>
+      <c r="AR12" s="5" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="AS12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AT12" s="7" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="AU12" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13 03:16</t>
+      <c r="AT12" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="AU12" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>IRCTC_IND_20260731</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>ITC_IND_20260731</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="n">
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="inlineStr"/>
-      <c r="O13" s="5" t="inlineStr"/>
-      <c r="P13" s="5" t="inlineStr"/>
-      <c r="Q13" s="5" t="inlineStr"/>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="inlineStr"/>
-      <c r="T13" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.4%) · Rank #9 · Conf 71% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V13" s="5" t="n">
+      <c r="V13" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="W13" s="5" t="inlineStr"/>
-      <c r="X13" s="5" t="n">
+      <c r="W13" s="7" t="inlineStr"/>
+      <c r="X13" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Y13" s="5" t="n">
+      <c r="Y13" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="Z13" s="5" t="n">
+      <c r="Z13" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="AA13" s="5" t="inlineStr">
+      <c r="AA13" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AB13" s="5" t="n">
-        <v>515</v>
-      </c>
-      <c r="AC13" s="5" t="n">
-        <v>494.35</v>
-      </c>
-      <c r="AD13" s="5" t="n">
-        <v>499</v>
-      </c>
-      <c r="AE13" s="5" t="n">
-        <v>531</v>
-      </c>
-      <c r="AF13" s="5" t="n">
-        <v>489.25</v>
-      </c>
-      <c r="AG13" s="5" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="AH13" s="5" t="n">
-        <v>556.2</v>
-      </c>
-      <c r="AI13" s="5" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="AJ13" s="5" t="n">
-        <v>595.1340000000001</v>
-      </c>
-      <c r="AK13" s="5" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="AL13" s="5" t="n">
-        <v>515.05</v>
-      </c>
-      <c r="AM13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="5" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AO13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="5" t="inlineStr"/>
-      <c r="AR13" s="5" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="AS13" s="5" t="n">
+      <c r="AB13" s="7" t="n">
+        <v>276.1</v>
+      </c>
+      <c r="AC13" s="7" t="n">
+        <v>282.9</v>
+      </c>
+      <c r="AD13" s="7" t="n">
+        <v>269</v>
+      </c>
+      <c r="AE13" s="7" t="n">
+        <v>283</v>
+      </c>
+      <c r="AF13" s="7" t="n">
+        <v>262.295</v>
+      </c>
+      <c r="AG13" s="7" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="AH13" s="7" t="n">
+        <v>277</v>
+      </c>
+      <c r="AI13" s="7" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="AJ13" s="7" t="n">
+        <v>296.39</v>
+      </c>
+      <c r="AK13" s="7" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AL13" s="7" t="n">
+        <v>279</v>
+      </c>
+      <c r="AM13" s="7" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="AN13" s="7" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="AO13" s="7" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AP13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="7" t="inlineStr"/>
+      <c r="AR13" s="7" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AT13" s="5" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="AU13" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-13 03:16</t>
+      <c r="AT13" s="7" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="AU13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       <c r="Q14" s="7" t="inlineStr"/>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.8%) · Rank → 10→10 · Conf 66% · momentum → · 61d left · → BUY</t>
         </is>
       </c>
       <c r="S14" s="7" t="inlineStr"/>
@@ -2641,43 +2641,43 @@
         </is>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>412.6</v>
+        <v>409.3</v>
       </c>
       <c r="AC14" s="7" t="n">
         <v>411.3</v>
       </c>
       <c r="AD14" s="7" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AE14" s="7" t="n">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AF14" s="7" t="n">
-        <v>391.97</v>
+        <v>388.835</v>
       </c>
       <c r="AG14" s="7" t="n">
-        <v>-4.7</v>
+        <v>-5.46</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>445.6080000000001</v>
+        <v>442.044</v>
       </c>
       <c r="AI14" s="7" t="n">
-        <v>8.34</v>
+        <v>7.47</v>
       </c>
       <c r="AJ14" s="7" t="n">
-        <v>476.8005600000001</v>
+        <v>472.98708</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>15.93</v>
+        <v>15</v>
       </c>
       <c r="AL14" s="7" t="n">
         <v>412.6</v>
       </c>
       <c r="AM14" s="7" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="AN14" s="7" t="n">
-        <v>0.32</v>
+        <v>-0.49</v>
       </c>
       <c r="AO14" s="7" t="n">
         <v>0</v>
@@ -2695,281 +2695,281 @@
         <v>5</v>
       </c>
       <c r="AT14" s="7" t="n">
-        <v>8.34</v>
+        <v>7.47</v>
       </c>
       <c r="AU14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>HINDUNILVR_IND_20260813</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>ONGC_IND_20260813</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="n">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="K15" s="5" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr"/>
-      <c r="M15" s="5" t="inlineStr"/>
-      <c r="N15" s="5" t="inlineStr"/>
-      <c r="O15" s="5" t="inlineStr"/>
-      <c r="P15" s="5" t="inlineStr"/>
-      <c r="Q15" s="5" t="inlineStr"/>
-      <c r="R15" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #11 · Conf 65% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S15" s="5" t="inlineStr"/>
-      <c r="T15" s="5" t="n">
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.2%) · Rank #11 · Conf 65% · momentum → · 61d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V15" s="5" t="n">
+      <c r="V15" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="W15" s="5" t="inlineStr"/>
-      <c r="X15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5" t="n">
+      <c r="W15" s="7" t="inlineStr"/>
+      <c r="X15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="Z15" s="5" t="n">
+      <c r="Z15" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="AA15" s="5" t="inlineStr">
+      <c r="AA15" s="7" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AB15" s="5" t="n">
-        <v>2064.9</v>
-      </c>
-      <c r="AC15" s="5" t="n">
-        <v>2064.89990234375</v>
-      </c>
-      <c r="AD15" s="5" t="n">
-        <v>2001</v>
-      </c>
-      <c r="AE15" s="5" t="n">
-        <v>2128</v>
-      </c>
-      <c r="AF15" s="5" t="n">
-        <v>1961.655</v>
-      </c>
-      <c r="AG15" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH15" s="5" t="n">
-        <v>2230.092</v>
-      </c>
-      <c r="AI15" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ15" s="5" t="n">
-        <v>2386.19844</v>
-      </c>
-      <c r="AK15" s="5" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AL15" s="5" t="n">
-        <v>2064.9</v>
-      </c>
-      <c r="AM15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="5" t="inlineStr"/>
-      <c r="AP15" s="5" t="inlineStr"/>
-      <c r="AQ15" s="5" t="inlineStr"/>
-      <c r="AR15" s="5" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AS15" s="5" t="n">
+      <c r="AB15" s="7" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="AC15" s="7" t="n">
+        <v>239.0500030517578</v>
+      </c>
+      <c r="AD15" s="7" t="n">
+        <v>232</v>
+      </c>
+      <c r="AE15" s="7" t="n">
+        <v>247</v>
+      </c>
+      <c r="AF15" s="7" t="n">
+        <v>227.145</v>
+      </c>
+      <c r="AG15" s="7" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="AH15" s="7" t="n">
+        <v>258.228</v>
+      </c>
+      <c r="AI15" s="7" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AJ15" s="7" t="n">
+        <v>276.30396</v>
+      </c>
+      <c r="AK15" s="7" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AL15" s="7" t="n">
+        <v>239.45</v>
+      </c>
+      <c r="AM15" s="7" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="AN15" s="7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AO15" s="7" t="inlineStr"/>
+      <c r="AP15" s="7" t="inlineStr"/>
+      <c r="AQ15" s="7" t="inlineStr"/>
+      <c r="AR15" s="7" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="AS15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AT15" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU15" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-13 03:16</t>
+      <c r="AT15" s="7" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AU15" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>ONGC_IND_20260813</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>HINDUNILVR_IND_20260813</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>INDIA</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="7" t="n">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr"/>
-      <c r="Q16" s="7" t="inlineStr"/>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank #12 · Conf 65% · momentum → · 61d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr"/>
-      <c r="T16" s="7" t="n">
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank #12 · Conf 65% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="U16" s="7" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V16" s="7" t="n">
+      <c r="V16" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="W16" s="7" t="inlineStr"/>
-      <c r="X16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="7" t="n">
+      <c r="W16" s="5" t="inlineStr"/>
+      <c r="X16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="Z16" s="7" t="n">
+      <c r="Z16" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="AA16" s="7" t="inlineStr">
+      <c r="AA16" s="5" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="AB16" s="7" t="n">
-        <v>239.4</v>
-      </c>
-      <c r="AC16" s="7" t="n">
-        <v>239.4499969482422</v>
-      </c>
-      <c r="AD16" s="7" t="n">
-        <v>232</v>
-      </c>
-      <c r="AE16" s="7" t="n">
-        <v>247</v>
-      </c>
-      <c r="AF16" s="7" t="n">
-        <v>227.43</v>
-      </c>
-      <c r="AG16" s="7" t="n">
-        <v>-5.02</v>
-      </c>
-      <c r="AH16" s="7" t="n">
-        <v>258.552</v>
-      </c>
-      <c r="AI16" s="7" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="AJ16" s="7" t="n">
-        <v>276.6506400000001</v>
-      </c>
-      <c r="AK16" s="7" t="n">
-        <v>15.54</v>
-      </c>
-      <c r="AL16" s="7" t="n">
-        <v>239.45</v>
-      </c>
-      <c r="AM16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AO16" s="7" t="inlineStr"/>
-      <c r="AP16" s="7" t="inlineStr"/>
-      <c r="AQ16" s="7" t="inlineStr"/>
-      <c r="AR16" s="7" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="AS16" s="7" t="n">
+      <c r="AB16" s="5" t="n">
+        <v>2063</v>
+      </c>
+      <c r="AC16" s="5" t="n">
+        <v>2063</v>
+      </c>
+      <c r="AD16" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AE16" s="5" t="n">
+        <v>2126</v>
+      </c>
+      <c r="AF16" s="5" t="n">
+        <v>1959.85</v>
+      </c>
+      <c r="AG16" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH16" s="5" t="n">
+        <v>2228.04</v>
+      </c>
+      <c r="AI16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" s="5" t="n">
+        <v>2384.0028</v>
+      </c>
+      <c r="AK16" s="5" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="AL16" s="5" t="n">
+        <v>2064.9</v>
+      </c>
+      <c r="AM16" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AN16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="5" t="inlineStr"/>
+      <c r="AP16" s="5" t="inlineStr"/>
+      <c r="AQ16" s="5" t="inlineStr"/>
+      <c r="AR16" s="5" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AS16" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AT16" s="7" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="AU16" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13 03:16</t>
+      <c r="AT16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU16" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>2278.9</v>
       </c>
       <c r="AM17" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN17" s="5" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v>444.35</v>
       </c>
       <c r="AM18" s="5" t="n">
-        <v>0</v>
+        <v>-0.46</v>
       </c>
       <c r="AN18" s="5" t="n">
         <v>0</v>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
         <v>114.03</v>
       </c>
       <c r="AM19" s="5" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="AN19" s="5" t="n">
         <v>0</v>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
         <v>412.6</v>
       </c>
       <c r="AM20" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="AN20" s="5" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
         <v>279</v>
       </c>
       <c r="AM21" s="5" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="AN21" s="5" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AU21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
         <v>586.65</v>
       </c>
       <c r="AM22" s="5" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="AN22" s="5" t="n">
         <v>0</v>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AU22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -3937,7 +3937,7 @@
         <v>699.85</v>
       </c>
       <c r="AM23" s="5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AN23" s="5" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4071,10 +4071,10 @@
         <v>15</v>
       </c>
       <c r="AL24" s="5" t="n">
-        <v>126.3</v>
+        <v>126</v>
       </c>
       <c r="AM24" s="5" t="n">
-        <v>-0.24</v>
+        <v>-0.04</v>
       </c>
       <c r="AN24" s="5" t="n">
         <v>0</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="AU24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
         <v>5536</v>
       </c>
       <c r="AM25" s="5" t="n">
-        <v>0</v>
+        <v>-1.12</v>
       </c>
       <c r="AN25" s="5" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4348,7 @@
         <v>11550</v>
       </c>
       <c r="AM26" s="5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN26" s="5" t="n">
         <v>0</v>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AU26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
         <v>1366</v>
       </c>
       <c r="AM27" s="5" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="AN27" s="5" t="n">
         <v>0</v>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AU27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
         <v>388</v>
       </c>
       <c r="AM28" s="5" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="AN28" s="5" t="n">
         <v>0</v>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AU28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
         <v>406</v>
       </c>
       <c r="AM29" s="5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AN29" s="5" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AU29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -4881,10 +4881,10 @@
         <v>15</v>
       </c>
       <c r="AL30" s="5" t="n">
-        <v>2815</v>
+        <v>2780</v>
       </c>
       <c r="AM30" s="5" t="n">
-        <v>-1.24</v>
+        <v>2.12</v>
       </c>
       <c r="AN30" s="5" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AU30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         <v>1429.6</v>
       </c>
       <c r="AM31" s="5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="AN31" s="5" t="n">
         <v>0</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AU31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
         <v>1942</v>
       </c>
       <c r="AM32" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AN32" s="5" t="n">
         <v>0</v>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AU32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5307,7 @@
         <v>2278.9</v>
       </c>
       <c r="AM33" s="5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN33" s="5" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AU33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
         <v>1685.8</v>
       </c>
       <c r="AM34" s="5" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AN34" s="5" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AU34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
         <v>338.45</v>
       </c>
       <c r="AM35" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AN35" s="5" t="n">
         <v>0</v>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AU35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5727,10 +5727,10 @@
         <v>15</v>
       </c>
       <c r="AL36" s="5" t="n">
-        <v>393.5</v>
+        <v>392.9</v>
       </c>
       <c r="AM36" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.61</v>
       </c>
       <c r="AN36" s="5" t="n">
         <v>0</v>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AU36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
         <v>267.95</v>
       </c>
       <c r="AM37" s="5" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN37" s="5" t="n">
         <v>0</v>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AU37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
         <v>515.05</v>
       </c>
       <c r="AM38" s="5" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
       <c r="AN38" s="5" t="n">
         <v>0</v>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AU38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
         <v>405.85</v>
       </c>
       <c r="AM39" s="5" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AN39" s="5" t="n">
         <v>0</v>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AU39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
         <v>412.6</v>
       </c>
       <c r="AM40" s="5" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="AN40" s="5" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AU40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -6428,10 +6428,10 @@
         <v>15</v>
       </c>
       <c r="AL41" s="5" t="n">
-        <v>5623.5</v>
+        <v>5598</v>
       </c>
       <c r="AM41" s="5" t="n">
-        <v>-0.45</v>
+        <v>0.85</v>
       </c>
       <c r="AN41" s="5" t="n">
         <v>0</v>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AU41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
         <v>380</v>
       </c>
       <c r="AM42" s="5" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AN42" s="5" t="n">
         <v>0</v>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AU42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:16</t>
+          <t>2026-08-13 03:50</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-13.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-13.xlsx
@@ -905,7 +905,7 @@
       </c>
       <c r="AU2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AU3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="AU4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AU5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AU6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="AU7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AU9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AU10" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AU11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AU12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AU13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AU14" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AU15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AU16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AU17" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="AU18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AU19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AU20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AU21" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AU22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="AU23" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="AU24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AU25" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       </c>
       <c r="AU26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="AU27" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AU28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AU29" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="AU30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AU31" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AU32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="AU33" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AU34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AU35" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="AU36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AU37" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="AU38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AU39" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AU40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AU41" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="AU42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13 03:50</t>
+          <t>2026-08-13 04:32</t>
         </is>
       </c>
     </row>
